--- a/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260710.xlsx
+++ b/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260710.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>INFUSOL N/S 500ML ( SODIUM CHLORIDE 0.9% W/V ) AIN MEDICARE</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1226,20 +1226,20 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="26">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
+          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1264,20 +1264,20 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.78</v>
+        <v>3.4</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>35.88</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="27">
@@ -1286,19 +1286,15 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>TABS BETAMETHASONE 0.5MG Y.S.P.</t>
+          <t>INFUSOL N/S 500ML ( SODIUM CHLORIDE 0.9% W/V ) AIN MEDICARE</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>UMH Pharmacy</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>088-215317  |  umhpharmacy@gmail.com</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1306,20 +1302,20 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="G27" s="8" t="n">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
+          <t>TAB NUELIN SR (THEOPHYLLINE) 250MG INOVA</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1348,16 +1344,16 @@
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.23</v>
+        <v>0.78</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>11.5</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="29">
@@ -1366,17 +1362,17 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>TAB LUSEFI ( LUSEOGLIFLOZIN ) 5MG TAISHO</t>
+          <t>TABS BETAMETHASONE 0.5MG Y.S.P.</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Zuellig Pharma</t>
+          <t>UMH Pharmacy</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>088-423500</t>
+          <t>088-215317  |  umhpharmacy@gmail.com</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -1390,16 +1386,16 @@
         </is>
       </c>
       <c r="G29" s="8" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>2.5</v>
+        <v>0.11</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>150</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="30">
@@ -1408,12 +1404,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>TAB LAZINE (LEVOCETIRIZINE DIHCl) 5MG SYNERRV</t>
+          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1428,16 +1424,16 @@
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="31">
@@ -1446,15 +1442,19 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>TAB LUSEFI ( LUSEOGLIFLOZIN ) 5MG TAISHO</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr"/>
+          <t>Zuellig Pharma</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>088-423500</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G31" s="8" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>96.2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>TAB LAZINE (LEVOCETIRIZINE DIHCl) 5MG SYNERRV</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1504,16 +1504,16 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>48.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>PULMICORT (BUDESONIDE) RESPULE 1MG ASTRAZENECA</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -1538,20 +1538,20 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>RESPULE</t>
         </is>
       </c>
       <c r="G33" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1.53</v>
+        <v>10.26</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>30.6</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="34">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1576,20 +1576,20 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>6.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="35">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -1618,16 +1618,16 @@
         </is>
       </c>
       <c r="G35" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>100</v>
-      </c>
       <c r="I35" s="10" t="n">
-        <v>0.68</v>
+        <v>1.53</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>68</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="36">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1.44</v>
+        <v>0.68</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>28.8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37">
@@ -1674,19 +1674,15 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Zuellig Pharma</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>088-423500</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1694,20 +1690,20 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G37" s="8" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>103.67</v>
+        <v>1.44</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>829.36</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="38">
@@ -1716,15 +1712,19 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>TAB DESLORATADINE 5MG SYNERRV</t>
+          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr"/>
+          <t>Zuellig Pharma</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>088-423500</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1732,20 +1732,20 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>0</v>
+        <v>103.67</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>0</v>
+        <v>829.36</v>
       </c>
     </row>
     <row r="39">
@@ -1754,19 +1754,15 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>CANDID (CLOTRIMAZOLE 1% W/W) CREAM  20G GLENMARK</t>
+          <t>TAB DESLORATADINE 5MG SYNERRV</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Pharmaforte</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>03-7805 2763  |  pfmy_orders@pharmafortegroup.com</t>
-        </is>
-      </c>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1774,20 +1770,20 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G39" s="8" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>9.390000000000001</v>
+        <v>0</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>9.390000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1796,15 +1792,19 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
+          <t>CANDID (CLOTRIMAZOLE 1% W/W) CREAM  20G GLENMARK</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr"/>
+          <t>Pharmaforte</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>03-7805 2763  |  pfmy_orders@pharmafortegroup.com</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1819,13 +1819,13 @@
         <v>1</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>12.33</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>61.65</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
+          <t>CANDID-B ( CLOTRIMAZOLE 1%W/W /BECLOMETHASONE 0.025%W/W ) CREAM 15G Y.S.P.</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G41" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>8.15</v>
+        <v>12.33</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>57.05</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="42">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
+          <t>INJ SHINCORT (TRIAMCINOLONE ACETONIDE 40MG/ML) 1ML VIAL Y.S.P.</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1888,20 +1888,20 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>7.05</v>
+        <v>8.15</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>35.25</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="43">
@@ -1910,19 +1910,15 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
+          <t>SYR FUCON (HYOSCINE-N-BUTYLBROMIDE) 1MG/ML 60ML Y.S.P.</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1934,16 +1930,16 @@
         </is>
       </c>
       <c r="G43" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>32</v>
+        <v>7.05</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>160</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="44">
@@ -1952,15 +1948,19 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>DIFFLAM FORTE THROAT SPRAY  (BENZYDAMINE 0.3% W/V) ADULTS &amp; CHILD (&gt;6YRS) INOVA</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1972,16 +1972,16 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45">
@@ -1990,19 +1990,15 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2010,20 +2006,20 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G45" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>39.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -2032,15 +2028,19 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
+          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2048,20 +2048,20 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>1.82</v>
+        <v>7.9</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>54.6</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="47">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -2086,20 +2086,20 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G47" s="8" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>9.65</v>
+        <v>1.82</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>9.65</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="48">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>SYR TUSSIDEX (DEXTROMETHORPHAN 15MG/5ML) 90ML XEPA</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -2124,20 +2124,20 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>7</v>
+        <v>9.65</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>56</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="49">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>CREAM MOMATE (MOMETASONE 0.1% W/W) 15G GLENMARK</t>
+          <t>SYR TUSSIDEX (DEXTROMETHORPHAN 15MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -2162,20 +2162,20 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G49" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>44.5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
+          <t>CREAM MOMATE (MOMETASONE 0.1% W/W) 15G GLENMARK</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2204,16 +2204,16 @@
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>31.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="51">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
+          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -2238,20 +2238,20 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>JAR</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G51" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>51</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="52">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
+          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -2276,20 +2276,20 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>JAR</t>
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>76.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
+          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -2324,10 +2324,10 @@
         <v>9</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>2.32</v>
+        <v>8.5</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>20.88</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="54">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
+          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -2352,20 +2352,20 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>11.6</v>
+        <v>2.32</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>23.2</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="55">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -2390,20 +2390,20 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G55" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>219</v>
+        <v>11.6</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>1095</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="56">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -2428,48 +2428,86 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>219</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
           <t>AMPULE</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G57" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H57" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I56" s="7" t="n">
+      <c r="I57" s="10" t="n">
         <v>7.4</v>
       </c>
-      <c r="J56" s="7" t="n">
+      <c r="J57" s="10" t="n">
         <v>66.59999999999999</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="J57" s="12" t="n">
-        <v>5430.73</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Total line items: 47</t>
-        </is>
+      <c r="J58" s="12" t="n">
+        <v>5505.29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-10 05:03</t>
+          <t>Total line items: 48</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Generated: 2026-07-10 08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -2478,7 +2516,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A58:I58"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
